--- a/files/九龙-何文田-誉林.xlsx
+++ b/files/九龙-何文田-誉林.xlsx
@@ -1044,7 +1044,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1357,38 +1357,30 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>20295000</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>26916</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L12" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K12" s="5" t="n">
+        <v>20295000</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>26916</v>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
@@ -1397,7 +1389,7 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1494,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2024-03-28</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1564,7 +1556,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2024-03-28</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1626,7 +1618,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1758,7 +1750,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1820,7 +1812,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1882,7 +1874,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1944,7 +1936,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2024-01-24</t>
+          <t>2024-01-25</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -2006,7 +1998,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -2068,7 +2060,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -2130,7 +2122,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -2192,7 +2184,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -2254,7 +2246,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -2316,7 +2308,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -2378,7 +2370,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -2440,7 +2432,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2023-12-12</t>
+          <t>2023-12-13</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -2502,7 +2494,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2564,7 +2556,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2626,7 +2618,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2688,7 +2680,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2024-03-20</t>
+          <t>2024-03-21</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2750,7 +2742,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2023-12-12</t>
+          <t>2023-12-13</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2812,7 +2804,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2874,7 +2866,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2025-01-16</t>
+          <t>2025-01-17</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -2936,7 +2928,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -2998,7 +2990,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2024-03-26</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -3060,7 +3052,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -3122,7 +3114,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -3184,7 +3176,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2024-09-25</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -3246,7 +3238,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2023-12-10</t>
+          <t>2023-12-11</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -3308,7 +3300,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -3370,7 +3362,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2023-12-12</t>
+          <t>2023-12-13</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -3432,7 +3424,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -3494,7 +3486,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -3556,7 +3548,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -3618,7 +3610,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -3680,7 +3672,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -3742,7 +3734,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2024-01-25</t>
+          <t>2024-01-26</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -3804,7 +3796,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -3866,7 +3858,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2023-12-18</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -3928,7 +3920,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -3990,7 +3982,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -4052,7 +4044,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -4254,7 +4246,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -4360,7 +4352,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -4370,7 +4362,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>47</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -4501,7 +4493,7 @@
           <t>B | 1296呎 (3房)
 $3874万
 $29,895/呎
-(25年-11月-18日)</t>
+(25年-11月-19日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr"/>
@@ -4524,7 +4516,56 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C8" s="21" t="inlineStr">
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>B | 754呎 (3房)
+$2030万
+$26,916/呎
+(26年-07月-30日)</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>C | 494呎 (2房)
+$1240万
+$25,107/呎
+(26年-07月-09日)</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="inlineStr">
+        <is>
+          <t>D | 260呎 (开放式)
+$624万
+$23,992/呎
+(26年-05月-15日)</t>
+        </is>
+      </c>
+      <c r="F8" s="22" t="inlineStr">
+        <is>
+          <t>E | 640呎 (3房)
+$1550万
+$24,219/呎
+(26年-06月-24日)</t>
+        </is>
+      </c>
+      <c r="G8" s="20" t="inlineStr"/>
+      <c r="H8" s="20" t="inlineStr"/>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>A | 699呎 (3房)
+$1765万
+$25,250/呎
+(26年-04月-27日)</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr">
         <is>
           <t>B | 754呎 (3房)
 招标单位
@@ -4532,61 +4573,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D8" s="22" t="inlineStr">
-        <is>
-          <t>C | 494呎 (2房)
-$1240万
-$25,107/呎
-(26年-07月-08日)</t>
-        </is>
-      </c>
-      <c r="E8" s="22" t="inlineStr">
-        <is>
-          <t>D | 260呎 (开放式)
-$624万
-$23,992/呎
-(26年-05月-14日)</t>
-        </is>
-      </c>
-      <c r="F8" s="22" t="inlineStr">
-        <is>
-          <t>E | 640呎 (3房)
-$1550万
-$24,219/呎
-(26年-06月-23日)</t>
-        </is>
-      </c>
-      <c r="G8" s="20" t="inlineStr"/>
-      <c r="H8" s="20" t="inlineStr"/>
-    </row>
-    <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="19" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B9" s="22" t="inlineStr">
-        <is>
-          <t>A | 699呎 (3房)
-$1765万
-$25,250/呎
-(26年-04月-26日)</t>
-        </is>
-      </c>
-      <c r="C9" s="21" t="inlineStr">
-        <is>
-          <t>B | 754呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
       <c r="D9" s="22" t="inlineStr">
         <is>
           <t>C | 494呎 (2房)
 $1165万
 $23,589/呎
-(26年-03月-04日)</t>
+(26年-03月-05日)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -4594,7 +4586,7 @@
           <t>D | 260呎 (开放式)
 $600万
 $23,077/呎
-(24年-03月-27日)</t>
+(24年-03月-28日)</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr">
@@ -4602,7 +4594,7 @@
           <t>E | 640呎 (3房)
 $1483万
 $23,177/呎
-(24年-03月-27日)</t>
+(24年-03月-28日)</t>
         </is>
       </c>
       <c r="G9" s="20" t="inlineStr"/>
@@ -4619,7 +4611,7 @@
           <t>A | 699呎 (3房)
 $1667万
 $23,854/呎
-(24年-05月-02日)</t>
+(24年-05月-03日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -4627,7 +4619,7 @@
           <t>B | 755呎 (3房)
 $1796万
 $23,787/呎
-(26年-06月-07日)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -4635,7 +4627,7 @@
           <t>C | 494呎 (2房)
 $1090万
 $22,065/呎
-(24年-01月-24日)</t>
+(24年-01月-25日)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -4643,7 +4635,7 @@
           <t>D | 260呎 (开放式)
 $568万
 $21,846/呎
-(25年-05月-28日)</t>
+(25年-05月-29日)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -4651,7 +4643,7 @@
           <t>E | 640呎 (3房)
 $1305万
 $20,392/呎
-(25年-10月-01日)</t>
+(25年-10月-02日)</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr"/>
@@ -4668,7 +4660,7 @@
           <t>A | 699呎 (3房)
 $1634万
 $23,372/呎
-(26年-01月-26日)</t>
+(26年-01月-27日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -4676,7 +4668,7 @@
           <t>B | 755呎 (3房)
 $1766万
 $23,389/呎
-(26年-06月-14日)</t>
+(26年-06月-15日)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -4684,7 +4676,7 @@
           <t>C | 494呎 (2房)
 $1085万
 $21,964/呎
-(26年-01月-13日)</t>
+(26年-01月-14日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -4692,7 +4684,7 @@
           <t>D | 260呎 (开放式)
 $516万
 $19,846/呎
-(24年-09月-12日)</t>
+(24年-09月-13日)</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -4700,7 +4692,7 @@
           <t>E | 640呎 (3房)
 $1292万
 $20,194/呎
-(25年-10月-01日)</t>
+(25年-10月-02日)</t>
         </is>
       </c>
       <c r="G11" s="20" t="inlineStr"/>
@@ -4717,7 +4709,7 @@
           <t>A | 699呎 (3房)
 $1578万
 $22,579/呎
-(24年-03月-20日)</t>
+(24年-03月-21日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -4725,7 +4717,7 @@
           <t>B | 755呎 (3房)
 $1669万
 $22,103/呎
-(26年-04月-29日)</t>
+(26年-04月-30日)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -4733,7 +4725,7 @@
           <t>C | 494呎 (2房)
 $1066万
 $21,571/呎
-(25年-09月-28日)</t>
+(25年-09月-29日)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -4741,7 +4733,7 @@
           <t>D | 260呎 (开放式)
 $503万
 $19,362/呎
-(24年-09月-12日)</t>
+(24年-09月-13日)</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -4749,7 +4741,7 @@
           <t>E | 640呎 (3房)
 $1388万
 $21,681/呎
-(23年-12月-12日)</t>
+(23年-12月-13日)</t>
         </is>
       </c>
       <c r="G12" s="20" t="inlineStr"/>
@@ -4766,7 +4758,7 @@
           <t>A | 699呎 (3房)
 $1562万
 $22,346/呎
-(24年-03月-26日)</t>
+(24年-03月-27日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -4774,7 +4766,7 @@
           <t>B | 755呎 (3房)
 $1818万
 $24,083/呎
-(24年-04月-21日)</t>
+(24年-04月-22日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -4782,7 +4774,7 @@
           <t>C | 494呎 (2房)
 $974万
 $19,717/呎
-(25年-01月-16日)</t>
+(25年-01月-17日)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -4790,7 +4782,7 @@
           <t>D | 260呎 (开放式)
 $484万
 $18,608/呎
-(24年-09月-12日)</t>
+(24年-09月-13日)</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
@@ -4798,7 +4790,7 @@
           <t>E | 624呎 (3房)
 $1277万
 $20,465/呎
-(23年-12月-12日)</t>
+(23年-12月-13日)</t>
         </is>
       </c>
       <c r="G13" s="20" t="inlineStr"/>
@@ -4815,7 +4807,7 @@
           <t>A | 699呎 (3房)
 $1488万
 $21,289/呎
-(25年-12月-04日)</t>
+(25年-12月-05日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -4823,7 +4815,7 @@
           <t>B | 755呎 (3房)
 $1634万
 $21,648/呎
-(23年-12月-10日)</t>
+(23年-12月-11日)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -4831,7 +4823,7 @@
           <t>C | 494呎 (2房)
 $933万
 $18,889/呎
-(24年-09月-25日)</t>
+(24年-09月-26日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -4839,7 +4831,7 @@
           <t>D | 260呎 (开放式)
 $479万
 $18,412/呎
-(24年-09月-12日)</t>
+(24年-09月-13日)</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -4847,7 +4839,7 @@
           <t>E | 672呎 (3房)
 $1357万
 $20,199/呎
-(25年-06月-24日)</t>
+(25年-06月-25日)</t>
         </is>
       </c>
       <c r="G14" s="20" t="inlineStr"/>
@@ -4864,7 +4856,7 @@
           <t>A | 699呎 (3房)
 $1472万
 $21,060/呎
-(25年-11月-30日)</t>
+(25年-12月-01日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -4872,7 +4864,7 @@
           <t>B | 755呎 (3房)
 $1587万
 $21,021/呎
-(26年-02月-12日)</t>
+(26年-02月-13日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -4880,7 +4872,7 @@
           <t>C | 494呎 (2房)
 $924万
 $18,696/呎
-(24年-08月-29日)</t>
+(24年-08月-30日)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -4888,7 +4880,7 @@
           <t>D | 306呎 (1房)
 $587万
 $19,190/呎
-(23年-12月-12日)</t>
+(23年-12月-13日)</t>
         </is>
       </c>
       <c r="F15" s="20" t="inlineStr"/>
@@ -4906,7 +4898,7 @@
           <t>A | 699呎 (3房)
 $1485万
 $21,242/呎
-(25年-05月-29日)</t>
+(25年-05月-30日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -4914,7 +4906,7 @@
           <t>B | 755呎 (3房)
 $1729万
 $22,905/呎
-(24年-01月-25日)</t>
+(24年-01月-26日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -4922,7 +4914,7 @@
           <t>C | 494呎 (2房)
 $905万
 $18,312/呎
-(24年-04月-04日)</t>
+(24年-04月-05日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -4930,7 +4922,7 @@
           <t>D | 306呎 (1房)
 $594万
 $19,405/呎
-(24年-04月-08日)</t>
+(24年-04月-09日)</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr"/>
@@ -4948,7 +4940,7 @@
           <t>A | 699呎 (3房)
 $1470万
 $21,029/呎
-(24年-04月-08日)</t>
+(24年-04月-09日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -4956,7 +4948,7 @@
           <t>B | 755呎 (3房)
 $1554万
 $20,583/呎
-(26年-03月-31日)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -4964,7 +4956,7 @@
           <t>C | 494呎 (2房)
 $885万
 $17,909/呎
-(24年-04月-08日)</t>
+(24年-04月-09日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -4972,7 +4964,7 @@
           <t>D | 306呎 (1房)
 $562万
 $18,382/呎
-(23年-12月-18日)</t>
+(23年-12月-19日)</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr"/>
@@ -4990,7 +4982,7 @@
           <t>A | 657呎 (3房)
 $1550万
 $23,592/呎
-(26年-07月-06日)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">

--- a/files/九龙-何文田-誉林.xlsx
+++ b/files/九龙-何文田-誉林.xlsx
@@ -1300,7 +1300,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -4529,7 +4529,7 @@
           <t>C | 494呎 (2房)
 $1240万
 $25,107/呎
-(26年-07月-09日)</t>
+(26年-08月-04日)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">

--- a/files/九龙-何文田-誉林.xlsx
+++ b/files/九龙-何文田-誉林.xlsx
@@ -1353,7 +1353,7 @@
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -1362,14 +1362,14 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
         <v>20295000</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>26916</v>
+        <v>26881</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>20295000</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>26916</v>
+        <v>26881</v>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
@@ -4518,10 +4518,10 @@
       </c>
       <c r="C8" s="22" t="inlineStr">
         <is>
-          <t>B | 754呎 (3房)
+          <t>B | 755呎 (3房)
 $2030万
-$26,916/呎
-(26年-07月-30日)</t>
+$26,881/呎
+(26年-08月-17日)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
